--- a/assessment_forms/031_refresher_pre_test_assessment--assessment_forms.xlsx
+++ b/assessment_forms/031_refresher_pre_test_assessment--assessment_forms.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -437,13 +437,13 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E28"/>
+  <dimension ref="A1:E21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="17" customWidth="1" min="1" max="1"/>
     <col width="22" customWidth="1" min="2" max="2"/>
-    <col width="50" customWidth="1" min="3" max="3"/>
-    <col width="6" customWidth="1" min="4" max="4"/>
+    <col width="36" customWidth="1" min="3" max="3"/>
+    <col width="50" customWidth="1" min="4" max="4"/>
     <col width="10" customWidth="1" min="5" max="5"/>
   </cols>
   <sheetData>
@@ -525,13 +525,17 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>What is your current level of confidence with this topic?</t>
-        </is>
-      </c>
-      <c r="D4" t="inlineStr"/>
+          <t>Current Confidence Level</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>Please describe your level of confidence (e.g., high, medium, low)</t>
+        </is>
+      </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
@@ -548,13 +552,17 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>How many years of experience do you have with this topic?</t>
-        </is>
-      </c>
-      <c r="D5" t="inlineStr"/>
+          <t>Years of Experience</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>Please enter the number of years</t>
+        </is>
+      </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
@@ -571,13 +579,17 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>What is your primary source of information for this topic?</t>
-        </is>
-      </c>
-      <c r="D6" t="inlineStr"/>
+          <t>Primary Source of Information</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>Please select your primary source</t>
+        </is>
+      </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
@@ -594,13 +606,17 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>How often do you use this topic in your work?</t>
-        </is>
-      </c>
-      <c r="D7" t="inlineStr"/>
+          <t>Frequency of Use</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>Please select how often you use this topic</t>
+        </is>
+      </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
@@ -612,18 +628,22 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>expected_outcome_1</t>
+          <t>pre_test_question_5</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>What do you expect this workshop to cover?</t>
-        </is>
-      </c>
-      <c r="D8" t="inlineStr"/>
+          <t>Expected Outcomes</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>Please describe your expectations</t>
+        </is>
+      </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
@@ -635,18 +655,22 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>expected_outcome_2</t>
+          <t>pre_test_question_6</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>What skills or knowledge do you think you will gain from the workshop?</t>
-        </is>
-      </c>
-      <c r="D9" t="inlineStr"/>
+          <t>Expected Skills or Knowledge</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>Please list your expected skills or knowledge</t>
+        </is>
+      </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
@@ -658,18 +682,22 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>pre_test_question_5</t>
+          <t>pre_test_question_7</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>How many hours of instruction will you need to reach your goal?</t>
-        </is>
-      </c>
-      <c r="D10" t="inlineStr"/>
+          <t>Hours of Instruction Needed</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>Please enter the number of hours</t>
+        </is>
+      </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
@@ -681,18 +709,22 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>pre_test_question_6</t>
+          <t>pre_test_question_8</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>What is your expected date of completion for this goal?</t>
-        </is>
-      </c>
-      <c r="D11" t="inlineStr"/>
+          <t>Expected Date of Completion</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>Please enter the date in YYYY-MM-DD format</t>
+        </is>
+      </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
@@ -704,202 +736,238 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>pre_test_question_7</t>
+          <t>pre_test_question_9</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>What is your expected completion status of this goal?</t>
-        </is>
-      </c>
-      <c r="D12" t="inlineStr"/>
+          <t>Expected Completion Status</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>Please select your expected completion status</t>
+        </is>
+      </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>select_multiple</t>
+          <t>date</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>pre_test_question_8</t>
+          <t>pre_test_question_10</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>What is your expected completion status of this goal?</t>
-        </is>
-      </c>
-      <c r="D13" t="inlineStr"/>
+          <t>Expected Date of Completion Status</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>Please enter the date in YYYY-MM-DD format</t>
+        </is>
+      </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>date</t>
+          <t>select_multiple</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>pre_test_question_9</t>
+          <t>pre_test_question_11</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>What is the date of your expected completion status of this goal?</t>
-        </is>
-      </c>
-      <c r="D14" t="inlineStr"/>
+          <t>Pre Test Question 11</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>Please select your expected skills or knowledge</t>
+        </is>
+      </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>select_one</t>
+          <t>text</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>pre_test_question_10</t>
+          <t>pre_test_question_12</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>What is your expected completion status of this goal?</t>
-        </is>
-      </c>
-      <c r="D15" t="inlineStr"/>
+          <t>Expected Duration</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>Please enter the number of weeks or months</t>
+        </is>
+      </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>select_multiple</t>
+          <t>text</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>pre_test_question_11</t>
+          <t>pre_test_question_13</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>What is your expected completion status of this goal?</t>
-        </is>
-      </c>
-      <c r="D16" t="inlineStr"/>
+          <t>Expected Budget</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>Please enter the budget in dollars</t>
+        </is>
+      </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>time</t>
+          <t>text</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>pre_test_question_12</t>
+          <t>pre_test_question_14</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>What is the date of your expected completion status of this goal?</t>
-        </is>
-      </c>
-      <c r="D17" t="inlineStr"/>
+          <t>Expected Location</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>Please describe your expected location</t>
+        </is>
+      </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>select_one</t>
+          <t>date</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>pre_test_question_13</t>
+          <t>pre_test_question_15</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>What is your expected completion status of this goal?</t>
-        </is>
-      </c>
-      <c r="D18" t="inlineStr"/>
+          <t>Expected Start Date</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>Please enter the date in YYYY-MM-DD format</t>
+        </is>
+      </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>select_multiple</t>
+          <t>date</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>pre_test_question_14</t>
+          <t>pre_test_question_16</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>What is your expected completion status of this goal?</t>
-        </is>
-      </c>
-      <c r="D19" t="inlineStr"/>
+          <t>Expected Completion Date</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>Please enter the date in YYYY-MM-DD format</t>
+        </is>
+      </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>date</t>
+          <t>select_multiple</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>pre_test_question_15</t>
+          <t>pre_test_question_17</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>What is the date of your expected completion status of this goal?</t>
-        </is>
-      </c>
-      <c r="D20" t="inlineStr"/>
+          <t>Expected Method of Completion</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>Please select your expected method of completion</t>
+        </is>
+      </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
@@ -911,179 +979,22 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>pre_test_question_16</t>
+          <t>pre_test_question_18</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>What is your expected completion status of this goal?</t>
-        </is>
-      </c>
-      <c r="D21" t="inlineStr"/>
+          <t>Expected Outcome</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>Please select your expected outcome</t>
+        </is>
+      </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" t="inlineStr">
-        <is>
-          <t>select_multiple</t>
-        </is>
-      </c>
-      <c r="B22" t="inlineStr">
-        <is>
-          <t>pre_test_question_17</t>
-        </is>
-      </c>
-      <c r="C22" t="inlineStr">
-        <is>
-          <t>What is your expected completion status of this goal?</t>
-        </is>
-      </c>
-      <c r="D22" t="inlineStr"/>
-      <c r="E22" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" t="inlineStr">
-        <is>
-          <t>time</t>
-        </is>
-      </c>
-      <c r="B23" t="inlineStr">
-        <is>
-          <t>pre_test_question_18</t>
-        </is>
-      </c>
-      <c r="C23" t="inlineStr">
-        <is>
-          <t>What is the date of your expected completion status of this goal?</t>
-        </is>
-      </c>
-      <c r="D23" t="inlineStr"/>
-      <c r="E23" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" t="inlineStr">
-        <is>
-          <t>select_one</t>
-        </is>
-      </c>
-      <c r="B24" t="inlineStr">
-        <is>
-          <t>pre_test_question_19</t>
-        </is>
-      </c>
-      <c r="C24" t="inlineStr">
-        <is>
-          <t>What is your expected completion status of this goal?</t>
-        </is>
-      </c>
-      <c r="D24" t="inlineStr"/>
-      <c r="E24" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" t="inlineStr">
-        <is>
-          <t>select_multiple</t>
-        </is>
-      </c>
-      <c r="B25" t="inlineStr">
-        <is>
-          <t>pre_test_question_20</t>
-        </is>
-      </c>
-      <c r="C25" t="inlineStr">
-        <is>
-          <t>What is your expected completion status of this goal?</t>
-        </is>
-      </c>
-      <c r="D25" t="inlineStr"/>
-      <c r="E25" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" t="inlineStr">
-        <is>
-          <t>date</t>
-        </is>
-      </c>
-      <c r="B26" t="inlineStr">
-        <is>
-          <t>pre_test_question_21</t>
-        </is>
-      </c>
-      <c r="C26" t="inlineStr">
-        <is>
-          <t>What is the date of your expected completion status of this goal?</t>
-        </is>
-      </c>
-      <c r="D26" t="inlineStr"/>
-      <c r="E26" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" t="inlineStr">
-        <is>
-          <t>select_one</t>
-        </is>
-      </c>
-      <c r="B27" t="inlineStr">
-        <is>
-          <t>pre_test_question_22</t>
-        </is>
-      </c>
-      <c r="C27" t="inlineStr">
-        <is>
-          <t>What is your expected completion status of this goal?</t>
-        </is>
-      </c>
-      <c r="D27" t="inlineStr"/>
-      <c r="E27" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" t="inlineStr">
-        <is>
-          <t>select_multiple</t>
-        </is>
-      </c>
-      <c r="B28" t="inlineStr">
-        <is>
-          <t>pre_test_question_23</t>
-        </is>
-      </c>
-      <c r="C28" t="inlineStr">
-        <is>
-          <t>What is your expected completion status of this goal?</t>
-        </is>
-      </c>
-      <c r="D28" t="inlineStr"/>
-      <c r="E28" t="inlineStr">
-        <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
@@ -1098,12 +1009,12 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C30"/>
+  <dimension ref="A1:C19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="30" customWidth="1" min="1" max="1"/>
-    <col width="9" customWidth="1" min="2" max="2"/>
-    <col width="9" customWidth="1" min="3" max="3"/>
+    <col width="10" customWidth="1" min="2" max="2"/>
+    <col width="10" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1131,12 +1042,12 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>option1</t>
+          <t>option_1</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>option1</t>
+          <t>Option 1</t>
         </is>
       </c>
     </row>
@@ -1148,12 +1059,12 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>option2</t>
+          <t>option_2</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>option2</t>
+          <t>Option 2</t>
         </is>
       </c>
     </row>
@@ -1165,12 +1076,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>option3</t>
+          <t>option_3</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>option3</t>
+          <t>Option 3</t>
         </is>
       </c>
     </row>
@@ -1182,12 +1093,12 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>option1</t>
+          <t>option_1</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>option1</t>
+          <t>Option 1</t>
         </is>
       </c>
     </row>
@@ -1199,114 +1110,114 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>option2</t>
+          <t>option_2</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>option2</t>
+          <t>Option 2</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>pre_test_question_7_choices</t>
+          <t>pre_test_question_4_choices</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>option1</t>
+          <t>option_3</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>option1</t>
+          <t>Option 3</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>pre_test_question_7_choices</t>
+          <t>pre_test_question_9_choices</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>option2</t>
+          <t>option_1</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>option2</t>
+          <t>Option 1</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>pre_test_question_8_choices</t>
+          <t>pre_test_question_9_choices</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>option1</t>
+          <t>option_2</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>option1</t>
+          <t>Option 2</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>pre_test_question_8_choices</t>
+          <t>pre_test_question_9_choices</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>option2</t>
+          <t>option_3</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>option2</t>
+          <t>Option 3</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>pre_test_question_10_choices</t>
+          <t>pre_test_question_11_choices</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>option1</t>
+          <t>option_1</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>option1</t>
+          <t>Option 1</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>pre_test_question_10_choices</t>
+          <t>pre_test_question_11_choices</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>option2</t>
+          <t>option_2</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>option2</t>
+          <t>Option 2</t>
         </is>
       </c>
     </row>
@@ -1318,301 +1229,114 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>option1</t>
+          <t>option_3</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>option1</t>
+          <t>Option 3</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>pre_test_question_11_choices</t>
+          <t>pre_test_question_17_choices</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>option2</t>
+          <t>option_1</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>option2</t>
+          <t>Option 1</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>pre_test_question_13_choices</t>
+          <t>pre_test_question_17_choices</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>option1</t>
+          <t>option_2</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>option1</t>
+          <t>Option 2</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>pre_test_question_13_choices</t>
+          <t>pre_test_question_17_choices</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>option2</t>
+          <t>option_3</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>option2</t>
+          <t>Option 3</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>pre_test_question_14_choices</t>
+          <t>pre_test_question_18_choices</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>option1</t>
+          <t>option_1</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>option1</t>
+          <t>Option 1</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>pre_test_question_14_choices</t>
+          <t>pre_test_question_18_choices</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>option2</t>
+          <t>option_2</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>option2</t>
+          <t>Option 2</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>pre_test_question_16_choices</t>
+          <t>pre_test_question_18_choices</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>option1</t>
+          <t>option_3</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>option1</t>
-        </is>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" t="inlineStr">
-        <is>
-          <t>pre_test_question_16_choices</t>
-        </is>
-      </c>
-      <c r="B20" t="inlineStr">
-        <is>
-          <t>option2</t>
-        </is>
-      </c>
-      <c r="C20" t="inlineStr">
-        <is>
-          <t>option2</t>
-        </is>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" t="inlineStr">
-        <is>
-          <t>pre_test_question_17_choices</t>
-        </is>
-      </c>
-      <c r="B21" t="inlineStr">
-        <is>
-          <t>option1</t>
-        </is>
-      </c>
-      <c r="C21" t="inlineStr">
-        <is>
-          <t>option1</t>
-        </is>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" t="inlineStr">
-        <is>
-          <t>pre_test_question_17_choices</t>
-        </is>
-      </c>
-      <c r="B22" t="inlineStr">
-        <is>
-          <t>option2</t>
-        </is>
-      </c>
-      <c r="C22" t="inlineStr">
-        <is>
-          <t>option2</t>
-        </is>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" t="inlineStr">
-        <is>
-          <t>pre_test_question_19_choices</t>
-        </is>
-      </c>
-      <c r="B23" t="inlineStr">
-        <is>
-          <t>option1</t>
-        </is>
-      </c>
-      <c r="C23" t="inlineStr">
-        <is>
-          <t>option1</t>
-        </is>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" t="inlineStr">
-        <is>
-          <t>pre_test_question_19_choices</t>
-        </is>
-      </c>
-      <c r="B24" t="inlineStr">
-        <is>
-          <t>option2</t>
-        </is>
-      </c>
-      <c r="C24" t="inlineStr">
-        <is>
-          <t>option2</t>
-        </is>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" t="inlineStr">
-        <is>
-          <t>pre_test_question_20_choices</t>
-        </is>
-      </c>
-      <c r="B25" t="inlineStr">
-        <is>
-          <t>option1</t>
-        </is>
-      </c>
-      <c r="C25" t="inlineStr">
-        <is>
-          <t>option1</t>
-        </is>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" t="inlineStr">
-        <is>
-          <t>pre_test_question_20_choices</t>
-        </is>
-      </c>
-      <c r="B26" t="inlineStr">
-        <is>
-          <t>option2</t>
-        </is>
-      </c>
-      <c r="C26" t="inlineStr">
-        <is>
-          <t>option2</t>
-        </is>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" t="inlineStr">
-        <is>
-          <t>pre_test_question_22_choices</t>
-        </is>
-      </c>
-      <c r="B27" t="inlineStr">
-        <is>
-          <t>option1</t>
-        </is>
-      </c>
-      <c r="C27" t="inlineStr">
-        <is>
-          <t>option1</t>
-        </is>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" t="inlineStr">
-        <is>
-          <t>pre_test_question_22_choices</t>
-        </is>
-      </c>
-      <c r="B28" t="inlineStr">
-        <is>
-          <t>option2</t>
-        </is>
-      </c>
-      <c r="C28" t="inlineStr">
-        <is>
-          <t>option2</t>
-        </is>
-      </c>
-    </row>
-    <row r="29">
-      <c r="A29" t="inlineStr">
-        <is>
-          <t>pre_test_question_23_choices</t>
-        </is>
-      </c>
-      <c r="B29" t="inlineStr">
-        <is>
-          <t>option1</t>
-        </is>
-      </c>
-      <c r="C29" t="inlineStr">
-        <is>
-          <t>option1</t>
-        </is>
-      </c>
-    </row>
-    <row r="30">
-      <c r="A30" t="inlineStr">
-        <is>
-          <t>pre_test_question_23_choices</t>
-        </is>
-      </c>
-      <c r="B30" t="inlineStr">
-        <is>
-          <t>option2</t>
-        </is>
-      </c>
-      <c r="C30" t="inlineStr">
-        <is>
-          <t>option2</t>
+          <t>Option 3</t>
         </is>
       </c>
     </row>
